--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/24.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/24.xlsx
@@ -426,13 +426,13 @@
         <v>-11.72238132671945</v>
       </c>
       <c r="E2">
-        <v>-10.28221477582968</v>
+        <v>-12.1788438451442</v>
       </c>
       <c r="F2">
-        <v>-4.600183613990239</v>
+        <v>-3.58215072554355</v>
       </c>
       <c r="G2">
-        <v>-6.918501708822213</v>
+        <v>-10.85189328585188</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.18920302250924</v>
       </c>
       <c r="E3">
-        <v>-9.843360359746343</v>
+        <v>-11.72467865844093</v>
       </c>
       <c r="F3">
-        <v>-4.47576200172235</v>
+        <v>-3.933250107383106</v>
       </c>
       <c r="G3">
-        <v>-7.911486601144449</v>
+        <v>-9.995335975203012</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.95941180290409</v>
       </c>
       <c r="E4">
-        <v>-9.944100792520977</v>
+        <v>-12.04412627189001</v>
       </c>
       <c r="F4">
-        <v>-4.483953726968634</v>
+        <v>-3.337161066165596</v>
       </c>
       <c r="G4">
-        <v>-6.761429565165953</v>
+        <v>-10.4129215684356</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.92476497544785</v>
       </c>
       <c r="E5">
-        <v>-10.95168625922763</v>
+        <v>-13.25544778420176</v>
       </c>
       <c r="F5">
-        <v>-4.291495814806614</v>
+        <v>-3.239507318151771</v>
       </c>
       <c r="G5">
-        <v>-6.954076831187222</v>
+        <v>-9.672746486219809</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.03227616189706</v>
       </c>
       <c r="E6">
-        <v>-11.07986018754073</v>
+        <v>-13.90463170404535</v>
       </c>
       <c r="F6">
-        <v>-4.32204600462186</v>
+        <v>-3.210302396998671</v>
       </c>
       <c r="G6">
-        <v>-8.63467858474378</v>
+        <v>-9.56931511193636</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.18552364785694</v>
       </c>
       <c r="E7">
-        <v>-11.96104688774529</v>
+        <v>-13.6137180053186</v>
       </c>
       <c r="F7">
-        <v>-4.142937233155954</v>
+        <v>-3.395358018049275</v>
       </c>
       <c r="G7">
-        <v>-7.252936329744928</v>
+        <v>-10.04828815110366</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.29394257881167</v>
       </c>
       <c r="E8">
-        <v>-13.37898908360501</v>
+        <v>-14.77097859492677</v>
       </c>
       <c r="F8">
-        <v>-3.851065292249159</v>
+        <v>-3.342749232664882</v>
       </c>
       <c r="G8">
-        <v>-7.490295823819594</v>
+        <v>-9.366143621645747</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.25769086699541</v>
       </c>
       <c r="E9">
-        <v>-13.7753075433343</v>
+        <v>-15.23085418735371</v>
       </c>
       <c r="F9">
-        <v>-3.742890449852377</v>
+        <v>-2.929118880690199</v>
       </c>
       <c r="G9">
-        <v>-7.280218535534062</v>
+        <v>-9.709569684253124</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.98873637276835</v>
       </c>
       <c r="E10">
-        <v>-13.58132583074173</v>
+        <v>-15.08588867742017</v>
       </c>
       <c r="F10">
-        <v>-3.441767301791117</v>
+        <v>-2.841899248482036</v>
       </c>
       <c r="G10">
-        <v>-7.078599691101369</v>
+        <v>-9.122629823413577</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.40815714031041</v>
       </c>
       <c r="E11">
-        <v>-14.01824205994978</v>
+        <v>-16.8106576296696</v>
       </c>
       <c r="F11">
-        <v>-3.753607038942394</v>
+        <v>-2.523485587622142</v>
       </c>
       <c r="G11">
-        <v>-7.759393517979253</v>
+        <v>-9.372191988345996</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.46105988691102</v>
       </c>
       <c r="E12">
-        <v>-14.55241179694656</v>
+        <v>-16.82225505160324</v>
       </c>
       <c r="F12">
-        <v>-3.44715914521594</v>
+        <v>-2.457800194417155</v>
       </c>
       <c r="G12">
-        <v>-6.820211611761252</v>
+        <v>-9.090461252408479</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.11329619485169</v>
       </c>
       <c r="E13">
-        <v>-15.43586726262897</v>
+        <v>-17.43527457802157</v>
       </c>
       <c r="F13">
-        <v>-3.092801794381173</v>
+        <v>-2.468328744106737</v>
       </c>
       <c r="G13">
-        <v>-6.502200607258862</v>
+        <v>-9.257196878493872</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.36694243589492</v>
       </c>
       <c r="E14">
-        <v>-17.0276304047991</v>
+        <v>-18.00893260836524</v>
       </c>
       <c r="F14">
-        <v>-2.622440700825766</v>
+        <v>-1.843230276443188</v>
       </c>
       <c r="G14">
-        <v>-6.847212421179548</v>
+        <v>-8.695158941200724</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.25190880442242</v>
       </c>
       <c r="E15">
-        <v>-15.54387589618591</v>
+        <v>-18.09850582423696</v>
       </c>
       <c r="F15">
-        <v>-2.475697072154639</v>
+        <v>-1.624244726573917</v>
       </c>
       <c r="G15">
-        <v>-6.422105268481735</v>
+        <v>-8.884134812218942</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.83031060499937</v>
       </c>
       <c r="E16">
-        <v>-16.84664088413454</v>
+        <v>-18.46254984971358</v>
       </c>
       <c r="F16">
-        <v>-2.234909720611087</v>
+        <v>-1.569110248978387</v>
       </c>
       <c r="G16">
-        <v>-6.251181802289163</v>
+        <v>-8.027984698671402</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.18993075278785</v>
       </c>
       <c r="E17">
-        <v>-16.87000781001412</v>
+        <v>-19.59820961830517</v>
       </c>
       <c r="F17">
-        <v>-2.295912352888049</v>
+        <v>-1.405435618961441</v>
       </c>
       <c r="G17">
-        <v>-5.448718805751985</v>
+        <v>-7.530019059745308</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.44618918598666</v>
       </c>
       <c r="E18">
-        <v>-17.59674184723907</v>
+        <v>-20.33640522324353</v>
       </c>
       <c r="F18">
-        <v>-1.647990706542567</v>
+        <v>-0.954396195076333</v>
       </c>
       <c r="G18">
-        <v>-4.924123138507994</v>
+        <v>-7.548925585320086</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.7202242753915</v>
       </c>
       <c r="E19">
-        <v>-19.46024965766149</v>
+        <v>-20.41593428376623</v>
       </c>
       <c r="F19">
-        <v>-1.930439968242518</v>
+        <v>-0.6538396503185884</v>
       </c>
       <c r="G19">
-        <v>-3.915853457430943</v>
+        <v>-7.149061342359216</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.128484387906546</v>
       </c>
       <c r="E20">
-        <v>-20.60704947231195</v>
+        <v>-21.79969102934205</v>
       </c>
       <c r="F20">
-        <v>-0.9811416934105206</v>
+        <v>-0.6251773098143226</v>
       </c>
       <c r="G20">
-        <v>-5.4574619565212</v>
+        <v>-7.559906664873849</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.770374826150409</v>
       </c>
       <c r="E21">
-        <v>-19.73598391151453</v>
+        <v>-22.439048160589</v>
       </c>
       <c r="F21">
-        <v>-0.695553747621363</v>
+        <v>-0.1254613606059097</v>
       </c>
       <c r="G21">
-        <v>-4.594141201335599</v>
+        <v>-7.120527750356238</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.721688866575371</v>
       </c>
       <c r="E22">
-        <v>-20.25601122418536</v>
+        <v>-23.19056200758392</v>
       </c>
       <c r="F22">
-        <v>-0.9154836363298262</v>
+        <v>0.07317120217657817</v>
       </c>
       <c r="G22">
-        <v>-4.70006541641012</v>
+        <v>-6.987073038577138</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.019041447716264</v>
       </c>
       <c r="E23">
-        <v>-20.22043100390709</v>
+        <v>-22.62971503020795</v>
       </c>
       <c r="F23">
-        <v>-1.003144788363681</v>
+        <v>0.2720332227296415</v>
       </c>
       <c r="G23">
-        <v>-4.512182025419862</v>
+        <v>-7.169523824337452</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.662973529088493</v>
       </c>
       <c r="E24">
-        <v>-21.60378924377023</v>
+        <v>-23.94008332601546</v>
       </c>
       <c r="F24">
-        <v>-0.0959284059613017</v>
+        <v>0.4562679316840711</v>
       </c>
       <c r="G24">
-        <v>-4.899032513865857</v>
+        <v>-6.440028562031349</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.627580129332104</v>
       </c>
       <c r="E25">
-        <v>-20.77655478289306</v>
+        <v>-23.81398343879787</v>
       </c>
       <c r="F25">
-        <v>-0.4486878360760684</v>
+        <v>0.1567576149560623</v>
       </c>
       <c r="G25">
-        <v>-4.434599390707042</v>
+        <v>-7.278007091113829</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.860768597363962</v>
       </c>
       <c r="E26">
-        <v>-22.65303214287345</v>
+        <v>-23.73449513454123</v>
       </c>
       <c r="F26">
-        <v>-0.2274980005479472</v>
+        <v>0.1758042666486313</v>
       </c>
       <c r="G26">
-        <v>-4.839326825065101</v>
+        <v>-7.086538379304541</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.294483972349159</v>
       </c>
       <c r="E27">
-        <v>-21.41593002803603</v>
+        <v>-23.99415783414105</v>
       </c>
       <c r="F27">
-        <v>-0.1391633858156163</v>
+        <v>0.2878890031866269</v>
       </c>
       <c r="G27">
-        <v>-6.116210860653077</v>
+        <v>-7.528459792796312</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.853845325130416</v>
       </c>
       <c r="E28">
-        <v>-22.15823295889935</v>
+        <v>-25.04609064680482</v>
       </c>
       <c r="F28">
-        <v>-0.02034650739506921</v>
+        <v>0.1074581573458525</v>
       </c>
       <c r="G28">
-        <v>-6.050671990612125</v>
+        <v>-7.261308699413745</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.474195582321645</v>
       </c>
       <c r="E29">
-        <v>-22.875937218953</v>
+        <v>-23.81548236369441</v>
       </c>
       <c r="F29">
-        <v>-0.01754082700178728</v>
+        <v>0.1388839315058574</v>
       </c>
       <c r="G29">
-        <v>-5.432338226423671</v>
+        <v>-7.336179997329903</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.094568300929568</v>
       </c>
       <c r="E30">
-        <v>-22.51027652825564</v>
+        <v>-25.52521678223837</v>
       </c>
       <c r="F30">
-        <v>-0.5567864686717926</v>
+        <v>0.2087459531557593</v>
       </c>
       <c r="G30">
-        <v>-5.482797561533243</v>
+        <v>-7.51665769794881</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.669710142340042</v>
       </c>
       <c r="E31">
-        <v>-22.14009189202462</v>
+        <v>-24.58572145071104</v>
       </c>
       <c r="F31">
-        <v>-0.633538022010778</v>
+        <v>0.04713644307399251</v>
       </c>
       <c r="G31">
-        <v>-5.540755282289263</v>
+        <v>-6.957486693092672</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.168264730751797</v>
       </c>
       <c r="E32">
-        <v>-21.28916898361333</v>
+        <v>-24.42160955267307</v>
       </c>
       <c r="F32">
-        <v>-0.3715328678119196</v>
+        <v>-0.2426065936076074</v>
       </c>
       <c r="G32">
-        <v>-6.303150746164643</v>
+        <v>-6.257657229363978</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.573944533397189</v>
       </c>
       <c r="E33">
-        <v>-22.00259383572973</v>
+        <v>-23.89699942430649</v>
       </c>
       <c r="F33">
-        <v>-0.5464161371561457</v>
+        <v>-0.2227208057360024</v>
       </c>
       <c r="G33">
-        <v>-5.371907528149815</v>
+        <v>-6.637532398358728</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.879385009246365</v>
       </c>
       <c r="E34">
-        <v>-20.77134250931023</v>
+        <v>-23.43936542651334</v>
       </c>
       <c r="F34">
-        <v>-0.8894977509040057</v>
+        <v>-0.1762220583146578</v>
       </c>
       <c r="G34">
-        <v>-5.008995594498289</v>
+        <v>-6.77043755957831</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.09241996841436</v>
       </c>
       <c r="E35">
-        <v>-20.98865491999031</v>
+        <v>-22.88756181173069</v>
       </c>
       <c r="F35">
-        <v>-0.4171750833387696</v>
+        <v>-0.3204582188575105</v>
       </c>
       <c r="G35">
-        <v>-5.983570543076637</v>
+        <v>-7.11647233207063</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.22561551473568</v>
       </c>
       <c r="E36">
-        <v>-21.02579746380123</v>
+        <v>-23.43974128985598</v>
       </c>
       <c r="F36">
-        <v>-0.1535736651547165</v>
+        <v>-0.3746748653707381</v>
       </c>
       <c r="G36">
-        <v>-4.094861275830415</v>
+        <v>-6.726000106804673</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.29438838943478</v>
       </c>
       <c r="E37">
-        <v>-21.72536971392816</v>
+        <v>-22.77700364730743</v>
       </c>
       <c r="F37">
-        <v>-0.5866996439542856</v>
+        <v>-0.5073304496224538</v>
       </c>
       <c r="G37">
-        <v>-5.026783155680794</v>
+        <v>-6.09361969789309</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.31219162709332</v>
       </c>
       <c r="E38">
-        <v>-21.4882316440425</v>
+        <v>-22.75058000147267</v>
       </c>
       <c r="F38">
-        <v>-0.3728176656536616</v>
+        <v>-0.5299158868597823</v>
       </c>
       <c r="G38">
-        <v>-4.198524388301614</v>
+        <v>-6.068611836889436</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.29219511820549</v>
       </c>
       <c r="E39">
-        <v>-20.38490970833968</v>
+        <v>-22.53454914893676</v>
       </c>
       <c r="F39">
-        <v>-0.8873878991290753</v>
+        <v>-0.5656939033540958</v>
       </c>
       <c r="G39">
-        <v>-4.350776377652696</v>
+        <v>-5.63502306652001</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.24288951038769</v>
       </c>
       <c r="E40">
-        <v>-19.97751912966164</v>
+        <v>-21.58001928370397</v>
       </c>
       <c r="F40">
-        <v>-0.9403454271900478</v>
+        <v>-0.7187347810213044</v>
       </c>
       <c r="G40">
-        <v>-2.584805586274952</v>
+        <v>-5.663642732707009</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.16631945726409</v>
       </c>
       <c r="E41">
-        <v>-20.14420772940998</v>
+        <v>-22.17557701434873</v>
       </c>
       <c r="F41">
-        <v>-0.8875411470985932</v>
+        <v>-0.6056709142131999</v>
       </c>
       <c r="G41">
-        <v>-3.205565980343692</v>
+        <v>-5.263513646102997</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.05946636156957</v>
       </c>
       <c r="E42">
-        <v>-19.45525927930504</v>
+        <v>-22.21449471997065</v>
       </c>
       <c r="F42">
-        <v>-1.266622779804717</v>
+        <v>-1.045944046964123</v>
       </c>
       <c r="G42">
-        <v>-3.393770494251259</v>
+        <v>-6.081099214663567</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.914258463326309</v>
       </c>
       <c r="E43">
-        <v>-19.02167147849262</v>
+        <v>-21.31787045187394</v>
       </c>
       <c r="F43">
-        <v>-1.106598764931908</v>
+        <v>-0.6617348200346704</v>
       </c>
       <c r="G43">
-        <v>-3.368845396886087</v>
+        <v>-4.8575944153508</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.72638253570906</v>
       </c>
       <c r="E44">
-        <v>-19.78537144904218</v>
+        <v>-20.21305411974859</v>
       </c>
       <c r="F44">
-        <v>-0.593729998101845</v>
+        <v>-1.006449145933448</v>
       </c>
       <c r="G44">
-        <v>-2.865341215272792</v>
+        <v>-5.09638737564397</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.49061113041949</v>
       </c>
       <c r="E45">
-        <v>-19.55446908786508</v>
+        <v>-20.63599094969497</v>
       </c>
       <c r="F45">
-        <v>-1.477461336267456</v>
+        <v>-1.054670069185213</v>
       </c>
       <c r="G45">
-        <v>-2.066129174455178</v>
+        <v>-5.011329529103476</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.206806656463948</v>
       </c>
       <c r="E46">
-        <v>-18.39746209280133</v>
+        <v>-20.74373240328546</v>
       </c>
       <c r="F46">
-        <v>-1.069086147096133</v>
+        <v>-0.8666836842635045</v>
       </c>
       <c r="G46">
-        <v>-2.789529722423482</v>
+        <v>-4.531373257911017</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.878535320145351</v>
       </c>
       <c r="E47">
-        <v>-17.42058420834069</v>
+        <v>-19.60781451167544</v>
       </c>
       <c r="F47">
-        <v>-1.521966203350262</v>
+        <v>-1.166650431430456</v>
       </c>
       <c r="G47">
-        <v>-2.270148164403844</v>
+        <v>-4.856773400057061</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.518178063833389</v>
       </c>
       <c r="E48">
-        <v>-18.33011009888525</v>
+        <v>-19.02135448531209</v>
       </c>
       <c r="F48">
-        <v>-1.579249465988653</v>
+        <v>-1.252652363556503</v>
       </c>
       <c r="G48">
-        <v>-3.200192964933455</v>
+        <v>-4.975813996558174</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.139364451275947</v>
       </c>
       <c r="E49">
-        <v>-17.64040539362103</v>
+        <v>-18.93568028556097</v>
       </c>
       <c r="F49">
-        <v>-2.039137510470466</v>
+        <v>-1.377191603995589</v>
       </c>
       <c r="G49">
-        <v>-2.206277809314685</v>
+        <v>-4.622115311142441</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.761066691453769</v>
       </c>
       <c r="E50">
-        <v>-16.88510574235569</v>
+        <v>-19.16265645977343</v>
       </c>
       <c r="F50">
-        <v>-1.837604005043374</v>
+        <v>-1.415678381897057</v>
       </c>
       <c r="G50">
-        <v>-2.656634492840519</v>
+        <v>-4.763773554767854</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.404100375966032</v>
       </c>
       <c r="E51">
-        <v>-17.60171411169949</v>
+        <v>-18.19418795154503</v>
       </c>
       <c r="F51">
-        <v>-1.843900425672053</v>
+        <v>-1.437215106002442</v>
       </c>
       <c r="G51">
-        <v>-3.288587841377535</v>
+        <v>-4.38300784902304</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.089990981558268</v>
       </c>
       <c r="E52">
-        <v>-17.48356169636536</v>
+        <v>-18.81602894533031</v>
       </c>
       <c r="F52">
-        <v>-2.014605409836558</v>
+        <v>-1.406043640635096</v>
       </c>
       <c r="G52">
-        <v>-2.45390330510663</v>
+        <v>-4.882552618171365</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.835100150619438</v>
       </c>
       <c r="E53">
-        <v>-16.93638165354455</v>
+        <v>-17.85010543949422</v>
       </c>
       <c r="F53">
-        <v>-1.936697455603265</v>
+        <v>-1.574327306881218</v>
       </c>
       <c r="G53">
-        <v>-2.069830364368083</v>
+        <v>-5.088640699082076</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.651961256918749</v>
       </c>
       <c r="E54">
-        <v>-16.92244301054894</v>
+        <v>-18.52309101872213</v>
       </c>
       <c r="F54">
-        <v>-2.089480711008203</v>
+        <v>-1.586254969114129</v>
       </c>
       <c r="G54">
-        <v>-2.260878636893884</v>
+        <v>-5.772589475858885</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.550284441750004</v>
       </c>
       <c r="E55">
-        <v>-16.64396450144725</v>
+        <v>-17.06207850657545</v>
       </c>
       <c r="F55">
-        <v>-2.317329792087429</v>
+        <v>-1.860462803523627</v>
       </c>
       <c r="G55">
-        <v>-3.006747857437222</v>
+        <v>-4.912744793489519</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.532196676249715</v>
       </c>
       <c r="E56">
-        <v>-16.8096568369139</v>
+        <v>-18.06459208239352</v>
       </c>
       <c r="F56">
-        <v>-2.194864783624953</v>
+        <v>-1.912022047408673</v>
       </c>
       <c r="G56">
-        <v>-2.443511502658858</v>
+        <v>-5.140679164413879</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.594866934907861</v>
       </c>
       <c r="E57">
-        <v>-16.67931829802513</v>
+        <v>-17.61054463601445</v>
       </c>
       <c r="F57">
-        <v>-2.227568728687478</v>
+        <v>-1.822357074627446</v>
       </c>
       <c r="G57">
-        <v>-3.106262856347714</v>
+        <v>-5.178214129738136</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.729754058162935</v>
       </c>
       <c r="E58">
-        <v>-16.3824496559783</v>
+        <v>-17.57576595563554</v>
       </c>
       <c r="F58">
-        <v>-2.142626278469611</v>
+        <v>-2.233200798659112</v>
       </c>
       <c r="G58">
-        <v>-3.194876228797386</v>
+        <v>-5.397537771714852</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.927614708852889</v>
       </c>
       <c r="E59">
-        <v>-14.96769097734597</v>
+        <v>-17.0802920290343</v>
       </c>
       <c r="F59">
-        <v>-2.304749376341114</v>
+        <v>-2.04764567206462</v>
       </c>
       <c r="G59">
-        <v>-2.176641805647129</v>
+        <v>-5.354451021521237</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.172638089825821</v>
       </c>
       <c r="E60">
-        <v>-14.38402954791936</v>
+        <v>-16.51664192624759</v>
       </c>
       <c r="F60">
-        <v>-2.321791378918908</v>
+        <v>-1.966425904954934</v>
       </c>
       <c r="G60">
-        <v>-3.057564731465034</v>
+        <v>-5.580385822939879</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.450298492940832</v>
       </c>
       <c r="E61">
-        <v>-14.26858516004182</v>
+        <v>-16.46984467585233</v>
       </c>
       <c r="F61">
-        <v>-2.437834883274882</v>
+        <v>-2.225432369155658</v>
       </c>
       <c r="G61">
-        <v>-3.303899114496665</v>
+        <v>-5.892017406188093</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.744450530274071</v>
       </c>
       <c r="E62">
-        <v>-14.31100790454567</v>
+        <v>-16.54388069740373</v>
       </c>
       <c r="F62">
-        <v>-2.795148677370241</v>
+        <v>-2.002516215960103</v>
       </c>
       <c r="G62">
-        <v>-2.603139387471436</v>
+        <v>-6.019152286532725</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.040417794338397</v>
       </c>
       <c r="E63">
-        <v>-16.04745579126088</v>
+        <v>-16.69185311407836</v>
       </c>
       <c r="F63">
-        <v>-2.593628425821593</v>
+        <v>-2.112949187896916</v>
       </c>
       <c r="G63">
-        <v>-3.192446288371561</v>
+        <v>-6.206211351683703</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.320844582139921</v>
       </c>
       <c r="E64">
-        <v>-15.18474073653361</v>
+        <v>-15.66264418398508</v>
       </c>
       <c r="F64">
-        <v>-2.886883740291063</v>
+        <v>-2.296289260056322</v>
       </c>
       <c r="G64">
-        <v>-3.385239218396558</v>
+        <v>-5.75508000050168</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.573610165715866</v>
       </c>
       <c r="E65">
-        <v>-14.9357108939038</v>
+        <v>-15.81500922044716</v>
       </c>
       <c r="F65">
-        <v>-3.360635341626129</v>
+        <v>-2.064901393432336</v>
       </c>
       <c r="G65">
-        <v>-2.977121785406284</v>
+        <v>-6.014193089314896</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.785335151320323</v>
       </c>
       <c r="E66">
-        <v>-14.64319864385234</v>
+        <v>-15.61596920238802</v>
       </c>
       <c r="F66">
-        <v>-2.323707392721583</v>
+        <v>-2.508516988653555</v>
       </c>
       <c r="G66">
-        <v>-3.950769781233637</v>
+        <v>-5.63952209790788</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.942921482845588</v>
       </c>
       <c r="E67">
-        <v>-14.24782663519066</v>
+        <v>-16.2174999902489</v>
       </c>
       <c r="F67">
-        <v>-2.737205205911818</v>
+        <v>-2.463776036860951</v>
       </c>
       <c r="G67">
-        <v>-3.363306854198886</v>
+        <v>-6.408098350305078</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.034997905561619</v>
       </c>
       <c r="E68">
-        <v>-14.35650095442673</v>
+        <v>-14.76028686779466</v>
       </c>
       <c r="F68">
-        <v>-2.688716719988949</v>
+        <v>-2.348336412341618</v>
       </c>
       <c r="G68">
-        <v>-3.436771170260853</v>
+        <v>-6.205238051295158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.058635772340939</v>
       </c>
       <c r="E69">
-        <v>-14.7549976101537</v>
+        <v>-15.36505098609702</v>
       </c>
       <c r="F69">
-        <v>-3.167377226553004</v>
+        <v>-2.670854633682383</v>
       </c>
       <c r="G69">
-        <v>-2.971619658720015</v>
+        <v>-5.892699378569183</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.021595652133382</v>
       </c>
       <c r="E70">
-        <v>-14.72054045142934</v>
+        <v>-14.94969482163948</v>
       </c>
       <c r="F70">
-        <v>-3.139187883835737</v>
+        <v>-2.68414247519069</v>
       </c>
       <c r="G70">
-        <v>-3.328029680932412</v>
+        <v>-5.912810942720255</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.934774908064457</v>
       </c>
       <c r="E71">
-        <v>-15.02171567225747</v>
+        <v>-16.35388404193791</v>
       </c>
       <c r="F71">
-        <v>-3.281064025648014</v>
+        <v>-2.683240383089041</v>
       </c>
       <c r="G71">
-        <v>-2.78722227218261</v>
+        <v>-6.302786586155323</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.809381330421544</v>
       </c>
       <c r="E72">
-        <v>-15.04834309942258</v>
+        <v>-15.49707864579065</v>
       </c>
       <c r="F72">
-        <v>-3.118332906102856</v>
+        <v>-2.888870165322976</v>
       </c>
       <c r="G72">
-        <v>-2.777449541750682</v>
+        <v>-5.806820516734949</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.653827978677883</v>
       </c>
       <c r="E73">
-        <v>-14.11871078428396</v>
+        <v>-16.08707993882799</v>
       </c>
       <c r="F73">
-        <v>-3.058974583120452</v>
+        <v>-2.506330098710165</v>
       </c>
       <c r="G73">
-        <v>-2.406185101703575</v>
+        <v>-5.792062104720878</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.477842847472171</v>
       </c>
       <c r="E74">
-        <v>-14.85233263047457</v>
+        <v>-16.18769357433041</v>
       </c>
       <c r="F74">
-        <v>-3.028035888993293</v>
+        <v>-2.692446858403755</v>
       </c>
       <c r="G74">
-        <v>-3.954173022048007</v>
+        <v>-4.849983471156015</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.286694186990154</v>
       </c>
       <c r="E75">
-        <v>-14.07029234019395</v>
+        <v>-15.95971660736227</v>
       </c>
       <c r="F75">
-        <v>-3.121551941830135</v>
+        <v>-2.741642770088615</v>
       </c>
       <c r="G75">
-        <v>-2.64168737973071</v>
+        <v>-4.904842521287279</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.086575049206626</v>
       </c>
       <c r="E76">
-        <v>-14.8917258258673</v>
+        <v>-16.43886538516585</v>
       </c>
       <c r="F76">
-        <v>-3.326546366266123</v>
+        <v>-2.991180994875341</v>
       </c>
       <c r="G76">
-        <v>-3.018871075202033</v>
+        <v>-4.941861041507409</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.882606045357166</v>
       </c>
       <c r="E77">
-        <v>-16.2462512717236</v>
+        <v>-16.7750049538072</v>
       </c>
       <c r="F77">
-        <v>-3.547928383031694</v>
+        <v>-3.134264067993497</v>
       </c>
       <c r="G77">
-        <v>-3.575678350543133</v>
+        <v>-5.619086100293958</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.683239236804085</v>
       </c>
       <c r="E78">
-        <v>-15.8466768391828</v>
+        <v>-17.49550328232359</v>
       </c>
       <c r="F78">
-        <v>-3.551849045949144</v>
+        <v>-2.956308383952287</v>
       </c>
       <c r="G78">
-        <v>-3.525463995803467</v>
+        <v>-5.099866759005744</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.494841310750763</v>
       </c>
       <c r="E79">
-        <v>-16.59952205753597</v>
+        <v>-17.69953367873918</v>
       </c>
       <c r="F79">
-        <v>-3.75145162696031</v>
+        <v>-3.062013034753921</v>
       </c>
       <c r="G79">
-        <v>-2.173344502290015</v>
+        <v>-4.972023421915709</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.326711660618149</v>
       </c>
       <c r="E80">
-        <v>-16.94676544444414</v>
+        <v>-18.32262000287657</v>
       </c>
       <c r="F80">
-        <v>-4.146636721976856</v>
+        <v>-3.100406207138872</v>
       </c>
       <c r="G80">
-        <v>-2.230550729208621</v>
+        <v>-4.940099831280516</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.186987977148788</v>
       </c>
       <c r="E81">
-        <v>-16.92802661900039</v>
+        <v>-19.62240072645414</v>
       </c>
       <c r="F81">
-        <v>-3.874688673842195</v>
+        <v>-3.219786375393323</v>
       </c>
       <c r="G81">
-        <v>-2.547552017321534</v>
+        <v>-4.330393348767402</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.081250220922877</v>
       </c>
       <c r="E82">
-        <v>-18.00444036214963</v>
+        <v>-20.0955130484055</v>
       </c>
       <c r="F82">
-        <v>-3.978523699415711</v>
+        <v>-3.127658666323573</v>
       </c>
       <c r="G82">
-        <v>-2.404586108208107</v>
+        <v>-4.654154770871507</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.011045626013615</v>
       </c>
       <c r="E83">
-        <v>-20.8027972897675</v>
+        <v>-20.63880766052774</v>
       </c>
       <c r="F83">
-        <v>-3.891841677651965</v>
+        <v>-3.465155427041759</v>
       </c>
       <c r="G83">
-        <v>-2.343046377178595</v>
+        <v>-5.040326597481952</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.97433549646091</v>
       </c>
       <c r="E84">
-        <v>-19.80636998301575</v>
+        <v>-20.42221527721487</v>
       </c>
       <c r="F84">
-        <v>-4.010219521349028</v>
+        <v>-3.217476887074318</v>
       </c>
       <c r="G84">
-        <v>-1.954153282134869</v>
+        <v>-4.645957860116272</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.968439380362944</v>
       </c>
       <c r="E85">
-        <v>-20.45996916501682</v>
+        <v>-21.47299332900669</v>
       </c>
       <c r="F85">
-        <v>-4.416041682184923</v>
+        <v>-3.757791951061337</v>
       </c>
       <c r="G85">
-        <v>-1.860544296466437</v>
+        <v>-4.186967273824018</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.984537823486543</v>
       </c>
       <c r="E86">
-        <v>-20.990239885893</v>
+        <v>-22.15752651695415</v>
       </c>
       <c r="F86">
-        <v>-4.509247925613117</v>
+        <v>-3.615523163100133</v>
       </c>
       <c r="G86">
-        <v>-2.066831010109504</v>
+        <v>-3.979207367415976</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.010894986832604</v>
       </c>
       <c r="E87">
-        <v>-23.03202466104938</v>
+        <v>-23.58358373823562</v>
       </c>
       <c r="F87">
-        <v>-4.357411494149579</v>
+        <v>-3.919418856858563</v>
       </c>
       <c r="G87">
-        <v>-2.366428760322468</v>
+        <v>-4.754457679620345</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.031457004194618</v>
       </c>
       <c r="E88">
-        <v>-23.85171015575578</v>
+        <v>-23.47779858541644</v>
       </c>
       <c r="F88">
-        <v>-4.547311407771755</v>
+        <v>-3.702050280159556</v>
       </c>
       <c r="G88">
-        <v>-1.538153440215591</v>
+        <v>-4.963005495866734</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.03244538864836</v>
       </c>
       <c r="E89">
-        <v>-25.08293431133123</v>
+        <v>-25.55708365383035</v>
       </c>
       <c r="F89">
-        <v>-4.437600772210183</v>
+        <v>-3.648109479991461</v>
       </c>
       <c r="G89">
-        <v>-2.38944698345702</v>
+        <v>-4.393204329283996</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.999817096472067</v>
       </c>
       <c r="E90">
-        <v>-26.20072019301454</v>
+        <v>-26.63159996637037</v>
       </c>
       <c r="F90">
-        <v>-4.229494171441877</v>
+        <v>-3.916150119087116</v>
       </c>
       <c r="G90">
-        <v>-1.736200206011412</v>
+        <v>-4.057670607242242</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.924716707016421</v>
       </c>
       <c r="E91">
-        <v>-27.72400375124069</v>
+        <v>-28.36519944293475</v>
       </c>
       <c r="F91">
-        <v>-4.623047382674907</v>
+        <v>-3.543047642294399</v>
       </c>
       <c r="G91">
-        <v>-1.947273968504264</v>
+        <v>-4.820370641307234</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.801763472969379</v>
       </c>
       <c r="E92">
-        <v>-30.33857256125726</v>
+        <v>-30.14373496707724</v>
       </c>
       <c r="F92">
-        <v>-4.676623701185772</v>
+        <v>-3.826717089178673</v>
       </c>
       <c r="G92">
-        <v>-2.884595348129193</v>
+        <v>-5.02788887789091</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.632055805746677</v>
       </c>
       <c r="E93">
-        <v>-32.72695768001272</v>
+        <v>-31.79907335584107</v>
       </c>
       <c r="F93">
-        <v>-4.862295627584058</v>
+        <v>-3.968334780361277</v>
       </c>
       <c r="G93">
-        <v>-1.782064503912475</v>
+        <v>-5.202851209641392</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.419620856817119</v>
       </c>
       <c r="E94">
-        <v>-33.80919730497283</v>
+        <v>-34.22110730071052</v>
       </c>
       <c r="F94">
-        <v>-4.761973708165816</v>
+        <v>-3.910771529540739</v>
       </c>
       <c r="G94">
-        <v>-1.770653053438607</v>
+        <v>-5.642481725619988</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.173971846171296</v>
       </c>
       <c r="E95">
-        <v>-33.75848066032393</v>
+        <v>-36.08256144817047</v>
       </c>
       <c r="F95">
-        <v>-4.341105910192874</v>
+        <v>-3.97491367427431</v>
       </c>
       <c r="G95">
-        <v>-3.154414741216413</v>
+        <v>-5.216205950346812</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.915151507356772</v>
       </c>
       <c r="E96">
-        <v>-38.44704754535044</v>
+        <v>-37.33789067088875</v>
       </c>
       <c r="F96">
-        <v>-4.819386196119044</v>
+        <v>-3.891427493950565</v>
       </c>
       <c r="G96">
-        <v>-2.822678214908205</v>
+        <v>-5.790161851581336</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.66198847353759</v>
       </c>
       <c r="E97">
-        <v>-38.53792722597338</v>
+        <v>-39.29509487276687</v>
       </c>
       <c r="F97">
-        <v>-4.950032161051568</v>
+        <v>-3.997669755196616</v>
       </c>
       <c r="G97">
-        <v>-3.525036935428901</v>
+        <v>-6.19087359420026</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.452561524315517</v>
       </c>
       <c r="E98">
-        <v>-42.09359444731599</v>
+        <v>-42.16626739819108</v>
       </c>
       <c r="F98">
-        <v>-4.659456615130154</v>
+        <v>-4.029269486511208</v>
       </c>
       <c r="G98">
-        <v>-4.074249819302913</v>
+        <v>-6.551262892150861</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.303308180873065</v>
       </c>
       <c r="E99">
-        <v>-44.05773400713687</v>
+        <v>-43.52539377363918</v>
       </c>
       <c r="F99">
-        <v>-5.308952159540954</v>
+        <v>-3.899381477752246</v>
       </c>
       <c r="G99">
-        <v>-4.418480344476331</v>
+        <v>-6.597113947869767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.265470365596491</v>
       </c>
       <c r="E100">
-        <v>-46.41494511082352</v>
+        <v>-45.98561860405233</v>
       </c>
       <c r="F100">
-        <v>-4.668153644492146</v>
+        <v>-4.056472243651741</v>
       </c>
       <c r="G100">
-        <v>-5.098396876786308</v>
+        <v>-7.411925279268427</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.321346440437265</v>
       </c>
       <c r="E101">
-        <v>-47.96780186855676</v>
+        <v>-47.35017009136161</v>
       </c>
       <c r="F101">
-        <v>-4.93234403189959</v>
+        <v>-3.689684411570565</v>
       </c>
       <c r="G101">
-        <v>-5.150004971198006</v>
+        <v>-6.970219051236708</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.538876944512431</v>
       </c>
       <c r="E102">
-        <v>-50.20318230389656</v>
+        <v>-49.75126776877511</v>
       </c>
       <c r="F102">
-        <v>-4.461300363604276</v>
+        <v>-3.856148154632737</v>
       </c>
       <c r="G102">
-        <v>-5.774357307176856</v>
+        <v>-7.842292888828142</v>
       </c>
     </row>
   </sheetData>
